--- a/data/napoli/service_status_grid.xlsx
+++ b/data/napoli/service_status_grid.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +56,24 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF00B050"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,12 +87,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -950,10 +981,25 @@
       <c r="A89" s="2" t="n">
         <v>46115</v>
       </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
         <v>46116</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
       </c>
     </row>
     <row r="91">
